--- a/data/xlsx/pksf--it-freelancing.xlsx
+++ b/data/xlsx/pksf--it-freelancing.xlsx
@@ -648,7 +648,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>7</v>
       </c>
@@ -670,7 +672,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>4</v>
       </c>
@@ -692,7 +696,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -715,7 +721,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -738,7 +746,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -761,7 +771,9 @@
       <c r="C21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -783,7 +795,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>3</v>
       </c>
@@ -805,7 +819,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>

--- a/data/xlsx/pksf--it-freelancing.xlsx
+++ b/data/xlsx/pksf--it-freelancing.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,7 +643,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -652,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -661,7 +667,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -676,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -685,7 +691,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -700,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -709,7 +715,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -734,7 +740,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -750,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -759,7 +765,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -784,7 +790,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -799,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -808,7 +814,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -832,7 +838,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -840,18 +846,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="10">
+      <c r="E24" s="15">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="15">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -860,7 +866,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -868,7 +874,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -877,11 +883,11 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
